--- a/Documentación/Documentos/Evidencias del proyecto.xlsx
+++ b/Documentación/Documentos/Evidencias del proyecto.xlsx
@@ -1059,8 +1059,8 @@
     <mergeCell ref="B3:B8"/>
     <mergeCell ref="B9:B16"/>
     <mergeCell ref="B17:B21"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="B25:B29"/>
-    <mergeCell ref="B22:B24"/>
   </mergeCells>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
